--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC9CE73-B0B6-40CD-A977-516A2B47D956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14DCB8BA-414F-4489-BAA2-5FDFD30A1D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="146">
   <si>
     <t>Paikkakunta</t>
   </si>
@@ -472,6 +472,9 @@
   </si>
   <si>
     <t>Vapaa-aikakeskus</t>
+  </si>
+  <si>
+    <t>3.10.2026</t>
   </si>
 </sst>
 </file>
@@ -619,11 +622,11 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1005,8 +1008,8 @@
       <c r="R1" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="S1" s="20">
-        <v>46286</v>
+      <c r="S1" s="24" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
@@ -1651,18 +1654,20 @@
       <c r="M18" s="8">
         <v>1</v>
       </c>
-      <c r="N18" s="8"/>
+      <c r="N18" s="8">
+        <v>1</v>
+      </c>
       <c r="O18" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P18" s="8">
         <f t="shared" si="0"/>
-        <v>185</v>
+        <v>370</v>
       </c>
       <c r="Q18" s="8">
         <f t="shared" si="1"/>
-        <v>370</v>
+        <v>740</v>
       </c>
       <c r="R18" s="8">
         <v>2</v>
@@ -4075,15 +4080,15 @@
       <c r="N71" s="6"/>
       <c r="O71" s="6">
         <f>SUM(O2:O70)</f>
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P71" s="6">
         <f>SUM(P2:P70)</f>
-        <v>13051</v>
+        <v>13236</v>
       </c>
       <c r="Q71" s="6">
         <f>SUM(Q2:Q70)</f>
-        <v>26102</v>
+        <v>26472</v>
       </c>
       <c r="R71" s="6"/>
     </row>
@@ -4141,7 +4146,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="7">
         <f>SUM(Q2:Q70)</f>
-        <v>26102</v>
+        <v>26472</v>
       </c>
       <c r="R72" s="13">
         <f>SUM(R2:R70)</f>
@@ -4384,11 +4389,11 @@
         <v>14</v>
       </c>
       <c r="C83" s="8">
-        <f>C2*2</f>
+        <f t="shared" ref="C83:C128" si="8">C2*2</f>
         <v>16</v>
       </c>
       <c r="D83" s="8">
-        <f>C83*D2</f>
+        <f t="shared" ref="D83:D91" si="9">C83*D2</f>
         <v>0</v>
       </c>
       <c r="E83" s="8">
@@ -4424,11 +4429,11 @@
         <v>16</v>
       </c>
       <c r="M83" s="8">
-        <f>C83*M2</f>
+        <f t="shared" ref="M83:M97" si="10">C83*M2</f>
         <v>32</v>
       </c>
       <c r="N83" s="8">
-        <f>C83*N2</f>
+        <f t="shared" ref="N83:N114" si="11">C83*N2</f>
         <v>0</v>
       </c>
       <c r="O83" s="8"/>
@@ -4450,11 +4455,11 @@
         <v>15</v>
       </c>
       <c r="C84" s="8">
-        <f>C3*2</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="D84" s="8">
-        <f>C84*D3</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E84" s="8">
@@ -4490,17 +4495,17 @@
         <v>0</v>
       </c>
       <c r="M84" s="8">
-        <f>C84*M3</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N84" s="8">
-        <f>C84*N3</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O84" s="8"/>
       <c r="P84" s="8"/>
       <c r="Q84" s="8">
-        <f t="shared" ref="Q84:Q149" si="8">SUM(D84:N84)</f>
+        <f t="shared" ref="Q84:Q149" si="12">SUM(D84:N84)</f>
         <v>4</v>
       </c>
       <c r="R84" s="8"/>
@@ -4513,11 +4518,11 @@
         <v>143</v>
       </c>
       <c r="C85" s="8">
-        <f>C4*2</f>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="D85" s="8">
-        <f>C85*D4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E85" s="8">
@@ -4553,17 +4558,17 @@
         <v>0</v>
       </c>
       <c r="M85" s="8">
-        <f>C85*M4</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N85" s="8">
-        <f>C85*N4</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O85" s="8"/>
       <c r="P85" s="8"/>
       <c r="Q85" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R85" s="8"/>
@@ -4572,15 +4577,15 @@
       <c r="A86" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B86" s="24" t="s">
+      <c r="B86" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C86" s="8">
-        <f>C5*2</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="D86" s="8">
-        <f>C86*D5</f>
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
       <c r="E86" s="8">
@@ -4616,17 +4621,17 @@
         <v>0</v>
       </c>
       <c r="M86" s="8">
-        <f>C86*M5</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N86" s="8">
-        <f>C86*N5</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O86" s="8"/>
       <c r="P86" s="8"/>
       <c r="Q86" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>80</v>
       </c>
       <c r="R86" s="8"/>
@@ -4639,11 +4644,11 @@
         <v>18</v>
       </c>
       <c r="C87" s="6">
-        <f>C6*2</f>
+        <f t="shared" si="8"/>
         <v>564</v>
       </c>
       <c r="D87" s="6">
-        <f>C87*D6</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E87" s="6">
@@ -4679,17 +4684,17 @@
         <v>0</v>
       </c>
       <c r="M87" s="14">
-        <f>C87*M6</f>
+        <f t="shared" si="10"/>
         <v>564</v>
       </c>
       <c r="N87" s="14">
-        <f>C87*N6</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O87" s="6"/>
       <c r="P87" s="14"/>
       <c r="Q87" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1128</v>
       </c>
       <c r="R87" s="6">
@@ -4705,57 +4710,57 @@
         <v>130</v>
       </c>
       <c r="C88" s="8">
-        <f>C7*2</f>
+        <f t="shared" si="8"/>
         <v>148</v>
       </c>
       <c r="D88" s="8">
-        <f>C88*D7</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E88" s="8">
-        <f t="shared" ref="E88:L88" si="9">D88*E7</f>
+        <f t="shared" ref="E88:L88" si="13">D88*E7</f>
         <v>0</v>
       </c>
       <c r="F88" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G88" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H88" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I88" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J88" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="K88" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L88" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M88" s="8">
-        <f>C88*M7</f>
+        <f t="shared" si="10"/>
         <v>148</v>
       </c>
       <c r="N88" s="8">
-        <f>C88*N7</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O88" s="8"/>
       <c r="P88" s="8"/>
       <c r="Q88" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>148</v>
       </c>
       <c r="R88" s="8">
@@ -4771,11 +4776,11 @@
         <v>20</v>
       </c>
       <c r="C89" s="14">
-        <f>C8*2</f>
+        <f t="shared" si="8"/>
         <v>278</v>
       </c>
       <c r="D89" s="14">
-        <f>C89*D8</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E89" s="14">
@@ -4807,21 +4812,21 @@
         <v>278</v>
       </c>
       <c r="L89" s="14">
-        <f>C89*L8</f>
+        <f t="shared" ref="L89:L97" si="14">C89*L8</f>
         <v>0</v>
       </c>
       <c r="M89" s="14">
-        <f>C89*M8</f>
+        <f t="shared" si="10"/>
         <v>834</v>
       </c>
       <c r="N89" s="14">
-        <f>C89*N8</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O89" s="14"/>
       <c r="P89" s="14"/>
       <c r="Q89" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1112</v>
       </c>
       <c r="R89" s="14">
@@ -4837,11 +4842,11 @@
         <v>21</v>
       </c>
       <c r="C90" s="14">
-        <f>C9*2</f>
+        <f t="shared" si="8"/>
         <v>282</v>
       </c>
       <c r="D90" s="14">
-        <f>C90*D9</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E90" s="14">
@@ -4873,21 +4878,21 @@
         <v>0</v>
       </c>
       <c r="L90" s="14">
-        <f>C90*L9</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M90" s="14">
-        <f>C90*M9</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N90" s="14">
-        <f>C90*N9</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O90" s="14"/>
       <c r="P90" s="14"/>
       <c r="Q90" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>282</v>
       </c>
       <c r="R90" s="14"/>
@@ -4900,11 +4905,11 @@
         <v>135</v>
       </c>
       <c r="C91" s="14">
-        <f>C10*2</f>
+        <f t="shared" si="8"/>
         <v>276</v>
       </c>
       <c r="D91" s="14">
-        <f>C91*D10</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E91" s="14">
@@ -4936,21 +4941,21 @@
         <v>0</v>
       </c>
       <c r="L91" s="14">
-        <f>C91*L10</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M91" s="14">
-        <f>C91*M10</f>
+        <f t="shared" si="10"/>
         <v>276</v>
       </c>
       <c r="N91" s="14">
-        <f>C91*N10</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O91" s="14"/>
       <c r="P91" s="14"/>
       <c r="Q91" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>276</v>
       </c>
       <c r="R91" s="14"/>
@@ -4963,7 +4968,7 @@
         <v>133</v>
       </c>
       <c r="C92" s="14">
-        <f>C11*2</f>
+        <f t="shared" si="8"/>
         <v>292</v>
       </c>
       <c r="D92" s="14">
@@ -4991,21 +4996,21 @@
         <v>0</v>
       </c>
       <c r="L92" s="14">
-        <f>C92*L11</f>
+        <f t="shared" si="14"/>
         <v>292</v>
       </c>
       <c r="M92" s="14">
-        <f>C92*M11</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N92" s="14">
-        <f>C92*N11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O92" s="14"/>
       <c r="P92" s="14"/>
       <c r="Q92" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>292</v>
       </c>
       <c r="R92" s="14"/>
@@ -5018,7 +5023,7 @@
         <v>23</v>
       </c>
       <c r="C93" s="8">
-        <f>C12*2</f>
+        <f t="shared" si="8"/>
         <v>66</v>
       </c>
       <c r="D93" s="8">
@@ -5054,21 +5059,21 @@
         <v>66</v>
       </c>
       <c r="L93" s="8">
-        <f>C93*L12</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M93" s="8">
-        <f>C93*M12</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N93" s="8">
-        <f>C93*N12</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O93" s="8"/>
       <c r="P93" s="8"/>
       <c r="Q93" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>66</v>
       </c>
       <c r="R93" s="8">
@@ -5084,7 +5089,7 @@
         <v>24</v>
       </c>
       <c r="C94" s="8">
-        <f>C13*2</f>
+        <f t="shared" si="8"/>
         <v>92</v>
       </c>
       <c r="D94" s="8">
@@ -5120,21 +5125,21 @@
         <v>0</v>
       </c>
       <c r="L94" s="8">
-        <f>C94*L13</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M94" s="8">
-        <f>C94*M13</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N94" s="8">
-        <f>C94*N13</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O94" s="8"/>
       <c r="P94" s="8"/>
       <c r="Q94" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>92</v>
       </c>
       <c r="R94" s="8"/>
@@ -5147,7 +5152,7 @@
         <v>25</v>
       </c>
       <c r="C95" s="8">
-        <f>C14*2</f>
+        <f t="shared" si="8"/>
         <v>84</v>
       </c>
       <c r="D95" s="8">
@@ -5183,21 +5188,21 @@
         <v>84</v>
       </c>
       <c r="L95" s="8">
-        <f>C95*L14</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M95" s="8">
-        <f>C95*M14</f>
+        <f t="shared" si="10"/>
         <v>840</v>
       </c>
       <c r="N95" s="8">
-        <f>C95*N14</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O95" s="8"/>
       <c r="P95" s="8"/>
       <c r="Q95" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>924</v>
       </c>
       <c r="R95" s="8"/>
@@ -5210,7 +5215,7 @@
         <v>26</v>
       </c>
       <c r="C96" s="8">
-        <f>C15*2</f>
+        <f t="shared" si="8"/>
         <v>120</v>
       </c>
       <c r="D96" s="8">
@@ -5246,21 +5251,21 @@
         <v>0</v>
       </c>
       <c r="L96" s="8">
-        <f>C96*L15</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M96" s="8">
-        <f>C96*M15</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N96" s="8">
-        <f>C96*N15</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
       <c r="Q96" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>120</v>
       </c>
       <c r="R96" s="8"/>
@@ -5273,7 +5278,7 @@
         <v>27</v>
       </c>
       <c r="C97" s="8">
-        <f>C16*2</f>
+        <f t="shared" si="8"/>
         <v>86</v>
       </c>
       <c r="D97" s="8">
@@ -5309,21 +5314,21 @@
         <v>0</v>
       </c>
       <c r="L97" s="8">
-        <f>C97*L16</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M97" s="8">
-        <f>C97*M16</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N97" s="8">
-        <f>C97*N16</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O97" s="8"/>
       <c r="P97" s="8"/>
       <c r="Q97" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>86</v>
       </c>
       <c r="R97" s="8"/>
@@ -5336,7 +5341,7 @@
         <v>126</v>
       </c>
       <c r="C98" s="14">
-        <f>C17*2</f>
+        <f t="shared" si="8"/>
         <v>364</v>
       </c>
       <c r="D98" s="14">
@@ -5371,13 +5376,13 @@
         <v>364</v>
       </c>
       <c r="N98" s="14">
-        <f>C98*N17</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O98" s="14"/>
       <c r="P98" s="14"/>
       <c r="Q98" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>364</v>
       </c>
       <c r="R98" s="14">
@@ -5393,11 +5398,11 @@
         <v>29</v>
       </c>
       <c r="C99" s="8">
-        <f>C18*2</f>
+        <f t="shared" si="8"/>
         <v>370</v>
       </c>
       <c r="D99" s="8">
-        <f>C99*D18</f>
+        <f t="shared" ref="D99:D109" si="15">C99*D18</f>
         <v>0</v>
       </c>
       <c r="E99" s="8">
@@ -5433,22 +5438,22 @@
         <v>0</v>
       </c>
       <c r="M99" s="8">
-        <f>C99*M18</f>
+        <f t="shared" ref="M99:M130" si="16">C99*M18</f>
         <v>370</v>
       </c>
       <c r="N99" s="8">
-        <f>C99*N18</f>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>370</v>
       </c>
       <c r="O99" s="8"/>
       <c r="P99" s="8"/>
       <c r="Q99" s="8">
-        <f t="shared" si="8"/>
-        <v>370</v>
+        <f t="shared" si="12"/>
+        <v>740</v>
       </c>
       <c r="R99" s="8">
         <f>SUM(Q99:Q100)</f>
-        <v>1202</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="100" spans="1:31" x14ac:dyDescent="0.3">
@@ -5459,11 +5464,11 @@
         <v>29</v>
       </c>
       <c r="C100" s="8">
-        <f>C19*2</f>
+        <f t="shared" si="8"/>
         <v>416</v>
       </c>
       <c r="D100" s="8">
-        <f>C100*D19</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E100" s="8">
@@ -5499,17 +5504,17 @@
         <v>416</v>
       </c>
       <c r="M100" s="8">
-        <f>C100*M19</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N100" s="8">
-        <f>C100*N19</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O100" s="8"/>
       <c r="P100" s="8"/>
       <c r="Q100" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>832</v>
       </c>
       <c r="R100" s="8"/>
@@ -5522,57 +5527,57 @@
         <v>132</v>
       </c>
       <c r="C101" s="14">
-        <f>C20*2</f>
+        <f t="shared" si="8"/>
         <v>236</v>
       </c>
       <c r="D101" s="14">
-        <f>C101*D20</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E101" s="14">
-        <f t="shared" ref="E101:L101" si="10">D101*E20</f>
+        <f t="shared" ref="E101:L101" si="17">D101*E20</f>
         <v>0</v>
       </c>
       <c r="F101" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="G101" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H101" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="I101" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="J101" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K101" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L101" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M101" s="14">
-        <f>C101*M20</f>
+        <f t="shared" si="16"/>
         <v>236</v>
       </c>
       <c r="N101" s="14">
-        <f>C101*N20</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O101" s="14"/>
       <c r="P101" s="14"/>
       <c r="Q101" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>236</v>
       </c>
       <c r="R101" s="14">
@@ -5588,57 +5593,57 @@
         <v>31</v>
       </c>
       <c r="C102" s="8">
-        <f>C21*2</f>
+        <f t="shared" si="8"/>
         <v>110</v>
       </c>
       <c r="D102" s="8">
-        <f>C102*D21</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E102" s="8">
-        <f>C102*E21</f>
+        <f t="shared" ref="E102:E109" si="18">C102*E21</f>
         <v>110</v>
       </c>
       <c r="F102" s="8">
-        <f>C102*F21</f>
+        <f t="shared" ref="F102:F109" si="19">C102*F21</f>
         <v>110</v>
       </c>
       <c r="G102" s="8">
-        <f>C102*G21</f>
+        <f t="shared" ref="G102:G109" si="20">C102*G21</f>
         <v>0</v>
       </c>
       <c r="H102" s="8">
-        <f>C102*H21</f>
+        <f t="shared" ref="H102:H109" si="21">C102*H21</f>
         <v>0</v>
       </c>
       <c r="I102" s="8">
-        <f>C102*I21</f>
+        <f t="shared" ref="I102:I109" si="22">C102*I21</f>
         <v>0</v>
       </c>
       <c r="J102" s="8">
-        <f>C102*J21</f>
+        <f t="shared" ref="J102:J109" si="23">C102*J21</f>
         <v>0</v>
       </c>
       <c r="K102" s="8">
-        <f>C102*K21</f>
+        <f t="shared" ref="K102:K109" si="24">C102*K21</f>
         <v>0</v>
       </c>
       <c r="L102" s="8">
-        <f>C102*L21</f>
+        <f t="shared" ref="L102:L109" si="25">C102*L21</f>
         <v>0</v>
       </c>
       <c r="M102" s="8">
-        <f>C102*M21</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N102" s="8">
-        <f>C102*N21</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O102" s="8"/>
       <c r="P102" s="8"/>
       <c r="Q102" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>220</v>
       </c>
       <c r="R102" s="8">
@@ -5654,57 +5659,57 @@
         <v>32</v>
       </c>
       <c r="C103" s="8">
-        <f>C22*2</f>
+        <f t="shared" si="8"/>
         <v>108</v>
       </c>
       <c r="D103" s="8">
-        <f>C103*D22</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E103" s="8">
-        <f>C103*E22</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F103" s="8">
-        <f>C103*F22</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="G103" s="8">
-        <f>C103*G22</f>
+        <f t="shared" si="20"/>
         <v>108</v>
       </c>
       <c r="H103" s="8">
-        <f>C103*H22</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="I103" s="8">
-        <f>C103*I22</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="J103" s="8">
-        <f>C103*J22</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="K103" s="8">
-        <f>C103*K22</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L103" s="8">
-        <f>C103*L22</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M103" s="8">
-        <f>C103*M22</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N103" s="8">
-        <f>C103*N22</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O103" s="8"/>
       <c r="P103" s="8"/>
       <c r="Q103" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>108</v>
       </c>
       <c r="R103" s="8"/>
@@ -5717,57 +5722,57 @@
         <v>33</v>
       </c>
       <c r="C104" s="8">
-        <f>C23*2</f>
+        <f t="shared" si="8"/>
         <v>110</v>
       </c>
       <c r="D104" s="8">
-        <f>C104*D23</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E104" s="8">
-        <f>C104*E23</f>
+        <f t="shared" si="18"/>
         <v>110</v>
       </c>
       <c r="F104" s="8">
-        <f>C104*F23</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="G104" s="8">
-        <f>C104*G23</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H104" s="8">
-        <f>C104*H23</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="I104" s="8">
-        <f>C104*I23</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="J104" s="8">
-        <f>C104*J23</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="K104" s="8">
-        <f>C104*K23</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L104" s="8">
-        <f>C104*L23</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M104" s="8">
-        <f>C104*M23</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N104" s="8">
-        <f>C104*N23</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O104" s="8"/>
       <c r="P104" s="8"/>
       <c r="Q104" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>110</v>
       </c>
       <c r="R104" s="8"/>
@@ -5780,57 +5785,57 @@
         <v>34</v>
       </c>
       <c r="C105" s="8">
-        <f>C24*2</f>
+        <f t="shared" si="8"/>
         <v>92</v>
       </c>
       <c r="D105" s="8">
-        <f>C105*D24</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E105" s="8">
-        <f>C105*E24</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F105" s="8">
-        <f>C105*F24</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="G105" s="8">
-        <f>C105*G24</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H105" s="8">
-        <f>C105*H24</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="I105" s="8">
-        <f>C105*I24</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="J105" s="8">
-        <f>C105*J24</f>
+        <f t="shared" si="23"/>
         <v>92</v>
       </c>
       <c r="K105" s="8">
-        <f>C105*K24</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L105" s="8">
-        <f>C105*L24</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M105" s="8">
-        <f>C105*M24</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N105" s="8">
-        <f>C105*N24</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O105" s="8"/>
       <c r="P105" s="8"/>
       <c r="Q105" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>92</v>
       </c>
       <c r="R105" s="8"/>
@@ -5843,57 +5848,57 @@
         <v>35</v>
       </c>
       <c r="C106" s="8">
-        <f>C25*2</f>
+        <f t="shared" si="8"/>
         <v>94</v>
       </c>
       <c r="D106" s="8">
-        <f>C106*D25</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E106" s="8">
-        <f>C106*E25</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F106" s="8">
-        <f>C106*F25</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="G106" s="8">
-        <f>C106*G25</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H106" s="8">
-        <f>C106*H25</f>
+        <f t="shared" si="21"/>
         <v>94</v>
       </c>
       <c r="I106" s="8">
-        <f>C106*I25</f>
+        <f t="shared" si="22"/>
         <v>188</v>
       </c>
       <c r="J106" s="8">
-        <f>C106*J25</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="K106" s="8">
-        <f>C106*K25</f>
+        <f t="shared" si="24"/>
         <v>94</v>
       </c>
       <c r="L106" s="8">
-        <f>C106*L25</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M106" s="8">
-        <f>C106*M25</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N106" s="8">
-        <f>C106*N25</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O106" s="8"/>
       <c r="P106" s="8"/>
       <c r="Q106" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>376</v>
       </c>
       <c r="R106" s="8"/>
@@ -5906,61 +5911,61 @@
         <v>101</v>
       </c>
       <c r="C107" s="14">
-        <f>C26*2</f>
+        <f t="shared" si="8"/>
         <v>800</v>
       </c>
       <c r="D107" s="14">
-        <f>C107*D26</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E107" s="14">
-        <f>C107*E26</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F107" s="14">
-        <f>C107*F26</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="G107" s="14">
-        <f>C107*G26</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H107" s="14">
-        <f>C107*H26</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="I107" s="14">
-        <f>C107*I26</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="J107" s="14">
-        <f>C107*J26</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="K107" s="14">
-        <f>C107*K26</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L107" s="14">
-        <f>C107*L26</f>
+        <f t="shared" si="25"/>
         <v>800</v>
       </c>
       <c r="M107" s="14">
-        <f>C107*M26</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N107" s="14">
-        <f>C107*N26</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O107" s="14"/>
       <c r="P107" s="14"/>
       <c r="Q107" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>800</v>
       </c>
       <c r="R107" s="14">
-        <f t="shared" ref="R107:R112" si="11">Q107</f>
+        <f t="shared" ref="R107:R112" si="26">Q107</f>
         <v>800</v>
       </c>
     </row>
@@ -5972,61 +5977,61 @@
         <v>37</v>
       </c>
       <c r="C108" s="8">
-        <f>C27*2</f>
+        <f t="shared" si="8"/>
         <v>726</v>
       </c>
       <c r="D108" s="8">
-        <f>C108*D27</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E108" s="8">
-        <f>C108*E27</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F108" s="8">
-        <f>C108*F27</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="G108" s="8">
-        <f>C108*G27</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H108" s="8">
-        <f>C108*H27</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="I108" s="8">
-        <f>C108*I27</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="J108" s="8">
-        <f>C108*J27</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="K108" s="8">
-        <f>C108*K27</f>
+        <f t="shared" si="24"/>
         <v>726</v>
       </c>
       <c r="L108" s="8">
-        <f>C108*L27</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M108" s="8">
-        <f>C108*M27</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N108" s="8">
-        <f>C108*N27</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O108" s="8"/>
       <c r="P108" s="8"/>
       <c r="Q108" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>726</v>
       </c>
       <c r="R108" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>726</v>
       </c>
       <c r="S108" s="17"/>
@@ -6051,57 +6056,57 @@
         <v>95</v>
       </c>
       <c r="C109" s="14">
-        <f>C28*2</f>
+        <f t="shared" si="8"/>
         <v>186</v>
       </c>
       <c r="D109" s="14">
-        <f>C109*D28</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E109" s="14">
-        <f>C109*E28</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F109" s="14">
-        <f>C109*F28</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="G109" s="14">
-        <f>C109*G28</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H109" s="14">
-        <f>C109*H28</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="I109" s="14">
-        <f>C109*I28</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="J109" s="14">
-        <f>C109*J28</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="K109" s="14">
-        <f>C109*K28</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L109" s="14">
-        <f>C109*L28</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M109" s="14">
-        <f>C109*M28</f>
+        <f t="shared" si="16"/>
         <v>186</v>
       </c>
       <c r="N109" s="14">
-        <f>C109*N28</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O109" s="14"/>
       <c r="P109" s="14"/>
       <c r="Q109" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>186</v>
       </c>
       <c r="R109" s="14">
@@ -6117,7 +6122,7 @@
         <v>123</v>
       </c>
       <c r="C110" s="8">
-        <f>C29*2</f>
+        <f t="shared" si="8"/>
         <v>348</v>
       </c>
       <c r="D110" s="8">
@@ -6148,17 +6153,17 @@
         <v>0</v>
       </c>
       <c r="M110" s="8">
-        <f>C110*M29</f>
+        <f t="shared" si="16"/>
         <v>348</v>
       </c>
       <c r="N110" s="8">
-        <f>C110*N29</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O110" s="8"/>
       <c r="P110" s="8"/>
       <c r="Q110" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>348</v>
       </c>
       <c r="R110" s="8">
@@ -6187,39 +6192,39 @@
         <v>100</v>
       </c>
       <c r="C111" s="14">
-        <f>C30*2</f>
+        <f t="shared" si="8"/>
         <v>418</v>
       </c>
       <c r="D111" s="14">
-        <f t="shared" ref="D111:K111" si="12">C111*D31</f>
+        <f t="shared" ref="D111:K111" si="27">C111*D31</f>
         <v>0</v>
       </c>
       <c r="E111" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F111" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="G111" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="H111" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I111" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J111" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="K111" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="L111" s="14">
@@ -6227,21 +6232,21 @@
         <v>418</v>
       </c>
       <c r="M111" s="14">
-        <f>C111*M30</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N111" s="14">
-        <f>C111*N30</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O111" s="14"/>
       <c r="P111" s="14"/>
       <c r="Q111" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>418</v>
       </c>
       <c r="R111" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>418</v>
       </c>
     </row>
@@ -6253,11 +6258,11 @@
         <v>39</v>
       </c>
       <c r="C112" s="8">
-        <f>C31*2</f>
+        <f t="shared" si="8"/>
         <v>516</v>
       </c>
       <c r="D112" s="8">
-        <f>C112*D31</f>
+        <f t="shared" ref="D112:D144" si="28">C112*D31</f>
         <v>0</v>
       </c>
       <c r="E112" s="8">
@@ -6273,7 +6278,7 @@
         <v>0</v>
       </c>
       <c r="H112" s="8">
-        <f>C112*H31</f>
+        <f t="shared" ref="H112:H144" si="29">C112*H31</f>
         <v>0</v>
       </c>
       <c r="I112" s="8">
@@ -6293,21 +6298,21 @@
         <v>0</v>
       </c>
       <c r="M112" s="8">
-        <f>C112*M31</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N112" s="8">
-        <f>C112*N31</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O112" s="8"/>
       <c r="P112" s="8"/>
       <c r="Q112" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>516</v>
       </c>
       <c r="R112" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="26"/>
         <v>516</v>
       </c>
       <c r="S112" s="17"/>
@@ -6332,11 +6337,11 @@
         <v>45</v>
       </c>
       <c r="C113" s="14">
-        <f>C32*2</f>
+        <f t="shared" si="8"/>
         <v>50</v>
       </c>
       <c r="D113" s="14">
-        <f>C113*D32</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E113" s="14">
@@ -6352,7 +6357,7 @@
         <v>0</v>
       </c>
       <c r="H113" s="14">
-        <f>C113*H32</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I113" s="14">
@@ -6372,17 +6377,17 @@
         <v>0</v>
       </c>
       <c r="M113" s="14">
-        <f>C113*M32</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N113" s="14">
-        <f>C113*N32</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O113" s="14"/>
       <c r="P113" s="14"/>
       <c r="Q113" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>100</v>
       </c>
       <c r="R113" s="14">
@@ -6398,11 +6403,11 @@
         <v>128</v>
       </c>
       <c r="C114" s="14">
-        <f>C33*2</f>
+        <f t="shared" si="8"/>
         <v>38</v>
       </c>
       <c r="D114" s="14">
-        <f>C114*D33</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E114" s="14">
@@ -6418,7 +6423,7 @@
         <v>0</v>
       </c>
       <c r="H114" s="14">
-        <f>C114*H33</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I114" s="14">
@@ -6438,17 +6443,17 @@
         <v>0</v>
       </c>
       <c r="M114" s="14">
-        <f>C114*M33</f>
+        <f t="shared" si="16"/>
         <v>38</v>
       </c>
       <c r="N114" s="14">
-        <f>C114*N33</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O114" s="14"/>
       <c r="P114" s="14"/>
       <c r="Q114" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>38</v>
       </c>
       <c r="R114" s="14"/>
@@ -6461,57 +6466,57 @@
         <v>46</v>
       </c>
       <c r="C115" s="14">
-        <f>C34*2</f>
+        <f t="shared" si="8"/>
         <v>54</v>
       </c>
       <c r="D115" s="14">
-        <f>C115*D34</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E115" s="14">
-        <f>C115*E34</f>
+        <f t="shared" ref="E115:E144" si="30">C115*E34</f>
         <v>0</v>
       </c>
       <c r="F115" s="14">
-        <f>C115*F34</f>
+        <f t="shared" ref="F115:F144" si="31">C115*F34</f>
         <v>0</v>
       </c>
       <c r="G115" s="14">
-        <f>C115*G34</f>
+        <f t="shared" ref="G115:G144" si="32">C115*G34</f>
         <v>54</v>
       </c>
       <c r="H115" s="14">
-        <f>C115*H34</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I115" s="14">
-        <f>C115*I34</f>
+        <f t="shared" ref="I115:I144" si="33">C115*I34</f>
         <v>54</v>
       </c>
       <c r="J115" s="14">
-        <f>C115*J34</f>
+        <f t="shared" ref="J115:J144" si="34">C115*J34</f>
         <v>108</v>
       </c>
       <c r="K115" s="14">
-        <f>C115*K34</f>
+        <f t="shared" ref="K115:K144" si="35">C115*K34</f>
         <v>0</v>
       </c>
       <c r="L115" s="14">
-        <f>C115*L34</f>
+        <f t="shared" ref="L115:L151" si="36">C115*L34</f>
         <v>0</v>
       </c>
       <c r="M115" s="14">
-        <f>C115*M34</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N115" s="14">
-        <f>C115*N34</f>
+        <f t="shared" ref="N115:N146" si="37">C115*N34</f>
         <v>0</v>
       </c>
       <c r="O115" s="19"/>
       <c r="P115" s="14"/>
       <c r="Q115" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>216</v>
       </c>
       <c r="R115" s="14"/>
@@ -6524,57 +6529,57 @@
         <v>47</v>
       </c>
       <c r="C116" s="14">
-        <f>C35*2</f>
+        <f t="shared" si="8"/>
         <v>54</v>
       </c>
       <c r="D116" s="14">
-        <f>C116*D35</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E116" s="14">
-        <f>C116*E35</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F116" s="14">
-        <f>C116*F35</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G116" s="14">
-        <f>C116*G35</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H116" s="14">
-        <f>C116*H35</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I116" s="14">
-        <f>C116*I35</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J116" s="14">
-        <f>C116*J35</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K116" s="14">
-        <f>C116*K35</f>
+        <f t="shared" si="35"/>
         <v>54</v>
       </c>
       <c r="L116" s="14">
-        <f>C116*L35</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M116" s="14">
-        <f>C116*M35</f>
+        <f t="shared" si="16"/>
         <v>432</v>
       </c>
       <c r="N116" s="14">
-        <f>C116*N35</f>
+        <f t="shared" si="37"/>
         <v>54</v>
       </c>
       <c r="O116" s="14"/>
       <c r="P116" s="14"/>
       <c r="Q116" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>540</v>
       </c>
       <c r="R116" s="14"/>
@@ -6587,57 +6592,57 @@
         <v>48</v>
       </c>
       <c r="C117" s="14">
-        <f>C36*2</f>
+        <f t="shared" si="8"/>
         <v>54</v>
       </c>
       <c r="D117" s="14">
-        <f>C117*D36</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E117" s="14">
-        <f>C117*E36</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F117" s="14">
-        <f>C117*F36</f>
+        <f t="shared" si="31"/>
         <v>54</v>
       </c>
       <c r="G117" s="14">
-        <f>C117*G36</f>
+        <f t="shared" si="32"/>
         <v>108</v>
       </c>
       <c r="H117" s="14">
-        <f>C117*H36</f>
+        <f t="shared" si="29"/>
         <v>54</v>
       </c>
       <c r="I117" s="14">
-        <f>C117*I36</f>
+        <f t="shared" si="33"/>
         <v>54</v>
       </c>
       <c r="J117" s="14">
-        <f>C117*J36</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K117" s="14">
-        <f>C117*K36</f>
+        <f t="shared" si="35"/>
         <v>54</v>
       </c>
       <c r="L117" s="14">
-        <f>C117*L36</f>
+        <f t="shared" si="36"/>
         <v>54</v>
       </c>
       <c r="M117" s="14">
-        <f>C117*M36</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N117" s="14">
-        <f>C117*N36</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O117" s="14"/>
       <c r="P117" s="14"/>
       <c r="Q117" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>378</v>
       </c>
       <c r="R117" s="14"/>
@@ -6650,57 +6655,57 @@
         <v>49</v>
       </c>
       <c r="C118" s="14">
-        <f>C37*2</f>
+        <f t="shared" si="8"/>
         <v>62</v>
       </c>
       <c r="D118" s="14">
-        <f>C118*D37</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E118" s="14">
-        <f>C118*E37</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F118" s="14">
-        <f>C118*F37</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G118" s="14">
-        <f>C118*G37</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H118" s="14">
-        <f>C118*H37</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I118" s="14">
-        <f>C118*I37</f>
+        <f t="shared" si="33"/>
         <v>62</v>
       </c>
       <c r="J118" s="14">
-        <f>C118*J37</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K118" s="14">
-        <f>C118*K37</f>
+        <f t="shared" si="35"/>
         <v>186</v>
       </c>
       <c r="L118" s="14">
-        <f>C118*L37</f>
+        <f t="shared" si="36"/>
         <v>124</v>
       </c>
       <c r="M118" s="14">
-        <f>C118*M37</f>
+        <f t="shared" si="16"/>
         <v>124</v>
       </c>
       <c r="N118" s="14">
-        <f>C118*N37</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O118" s="14"/>
       <c r="P118" s="14"/>
       <c r="Q118" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>496</v>
       </c>
       <c r="R118" s="14"/>
@@ -6713,57 +6718,57 @@
         <v>41</v>
       </c>
       <c r="C119" s="8">
-        <f>C38*2</f>
+        <f t="shared" si="8"/>
         <v>158</v>
       </c>
       <c r="D119" s="8">
-        <f>C119*D38</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E119" s="8">
-        <f>C119*E38</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F119" s="8">
-        <f>C119*F38</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G119" s="8">
-        <f>C119*G38</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H119" s="8">
-        <f>C119*H38</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I119" s="8">
-        <f>C119*I38</f>
+        <f t="shared" si="33"/>
         <v>158</v>
       </c>
       <c r="J119" s="8">
-        <f>C119*J38</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K119" s="8">
-        <f>C119*K38</f>
+        <f t="shared" si="35"/>
         <v>158</v>
       </c>
       <c r="L119" s="8">
-        <f>C119*L38</f>
+        <f t="shared" si="36"/>
         <v>158</v>
       </c>
       <c r="M119" s="8">
-        <f>C119*M38</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N119" s="8">
-        <f>C119*N38</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O119" s="8"/>
       <c r="P119" s="8"/>
       <c r="Q119" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>474</v>
       </c>
       <c r="R119" s="8">
@@ -6792,57 +6797,57 @@
         <v>42</v>
       </c>
       <c r="C120" s="8">
-        <f>C39*2</f>
+        <f t="shared" si="8"/>
         <v>140</v>
       </c>
       <c r="D120" s="8">
-        <f>C120*D39</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E120" s="8">
-        <f>C120*E39</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F120" s="8">
-        <f>C120*F39</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G120" s="8">
-        <f>C120*G39</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H120" s="8">
-        <f>C120*H39</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I120" s="8">
-        <f>C120*I39</f>
+        <f t="shared" si="33"/>
         <v>280</v>
       </c>
       <c r="J120" s="8">
-        <f>C120*J39</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K120" s="8">
-        <f>C120*K39</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L120" s="8">
-        <f>C120*L39</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M120" s="8">
-        <f>C120*M39</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N120" s="8">
-        <f>C120*N39</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O120" s="8"/>
       <c r="P120" s="8"/>
       <c r="Q120" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>280</v>
       </c>
       <c r="R120" s="8"/>
@@ -6868,57 +6873,57 @@
         <v>43</v>
       </c>
       <c r="C121" s="8">
-        <f>C40*2</f>
+        <f t="shared" si="8"/>
         <v>132</v>
       </c>
       <c r="D121" s="8">
-        <f>C121*D40</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E121" s="8">
-        <f>C121*E40</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F121" s="8">
-        <f>C121*F40</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G121" s="8">
-        <f>C121*G40</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H121" s="8">
-        <f>C121*H40</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I121" s="8">
-        <f>C121*I40</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J121" s="8">
-        <f>C121*J40</f>
+        <f t="shared" si="34"/>
         <v>132</v>
       </c>
       <c r="K121" s="8">
-        <f>C121*K40</f>
+        <f t="shared" si="35"/>
         <v>132</v>
       </c>
       <c r="L121" s="8">
-        <f>C121*L40</f>
+        <f t="shared" si="36"/>
         <v>132</v>
       </c>
       <c r="M121" s="8">
-        <f>C121*M40</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N121" s="8">
-        <f>C121*N40</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O121" s="8"/>
       <c r="P121" s="8"/>
       <c r="Q121" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>396</v>
       </c>
       <c r="R121" s="8"/>
@@ -6944,57 +6949,57 @@
         <v>51</v>
       </c>
       <c r="C122" s="14">
-        <f>C41*2</f>
+        <f t="shared" si="8"/>
         <v>840</v>
       </c>
       <c r="D122" s="14">
-        <f>C122*D41</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E122" s="14">
-        <f>C122*E41</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F122" s="14">
-        <f>C122*F41</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G122" s="14">
-        <f>C122*G41</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H122" s="14">
-        <f>C122*H41</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I122" s="14">
-        <f>C122*I41</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J122" s="14">
-        <f>C122*J41</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K122" s="14">
-        <f>C122*K41</f>
+        <f t="shared" si="35"/>
         <v>840</v>
       </c>
       <c r="L122" s="14">
-        <f>C122*L41</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M122" s="14">
-        <f>C122*M41</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N122" s="14">
-        <f>C122*N41</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O122" s="14"/>
       <c r="P122" s="14"/>
       <c r="Q122" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>840</v>
       </c>
       <c r="R122" s="14">
@@ -7010,57 +7015,57 @@
         <v>53</v>
       </c>
       <c r="C123" s="8">
-        <f>C42*2</f>
+        <f t="shared" si="8"/>
         <v>282</v>
       </c>
       <c r="D123" s="8">
-        <f>C123*D42</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E123" s="8">
-        <f>C123*E42</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F123" s="8">
-        <f>C123*F42</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G123" s="8">
-        <f>C123*G42</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H123" s="8">
-        <f>C123*H42</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I123" s="8">
-        <f>C123*I42</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J123" s="8">
-        <f>C123*J42</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K123" s="8">
-        <f>C123*K42</f>
+        <f t="shared" si="35"/>
         <v>282</v>
       </c>
       <c r="L123" s="8">
-        <f>C123*L42</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M123" s="8">
-        <f>C123*M42</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N123" s="8">
-        <f>C123*N42</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O123" s="8"/>
       <c r="P123" s="8"/>
       <c r="Q123" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>282</v>
       </c>
       <c r="R123" s="8">
@@ -7089,57 +7094,57 @@
         <v>55</v>
       </c>
       <c r="C124" s="14">
-        <f>C43*2</f>
+        <f t="shared" si="8"/>
         <v>160</v>
       </c>
       <c r="D124" s="14">
-        <f>C124*D43</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E124" s="14">
-        <f>C124*E43</f>
+        <f t="shared" si="30"/>
         <v>160</v>
       </c>
       <c r="F124" s="14">
-        <f>C124*F43</f>
+        <f t="shared" si="31"/>
         <v>160</v>
       </c>
       <c r="G124" s="14">
-        <f>C124*G43</f>
+        <f t="shared" si="32"/>
         <v>320</v>
       </c>
       <c r="H124" s="14">
-        <f>C124*H43</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I124" s="14">
-        <f>C124*I43</f>
+        <f t="shared" si="33"/>
         <v>480</v>
       </c>
       <c r="J124" s="14">
-        <f>C124*J43</f>
+        <f t="shared" si="34"/>
         <v>160</v>
       </c>
       <c r="K124" s="14">
-        <f>C124*K43</f>
+        <f t="shared" si="35"/>
         <v>160</v>
       </c>
       <c r="L124" s="14">
-        <f>C124*L43</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M124" s="14">
-        <f>C124*M43</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N124" s="14">
-        <f>C124*N43</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O124" s="14"/>
       <c r="P124" s="14"/>
       <c r="Q124" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1440</v>
       </c>
       <c r="R124" s="14">
@@ -7155,57 +7160,57 @@
         <v>119</v>
       </c>
       <c r="C125" s="8">
-        <f>C44*2</f>
+        <f t="shared" si="8"/>
         <v>1044</v>
       </c>
       <c r="D125" s="8">
-        <f>C125*D44</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E125" s="8">
-        <f>C125*E44</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F125" s="8">
-        <f>C125*F44</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G125" s="8">
-        <f>C125*G44</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H125" s="8">
-        <f>C125*H44</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I125" s="8">
-        <f>C125*I44</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J125" s="8">
-        <f>C125*J44</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K125" s="8">
-        <f>C125*K44</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L125" s="8">
-        <f>C125*L44</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M125" s="8">
-        <f>C125*M44</f>
+        <f t="shared" si="16"/>
         <v>2088</v>
       </c>
       <c r="N125" s="8">
-        <f>C125*N44</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O125" s="8"/>
       <c r="P125" s="8"/>
       <c r="Q125" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2088</v>
       </c>
       <c r="R125" s="8">
@@ -7234,57 +7239,57 @@
         <v>57</v>
       </c>
       <c r="C126" s="14">
-        <f>C45*2</f>
+        <f t="shared" si="8"/>
         <v>68</v>
       </c>
       <c r="D126" s="14">
-        <f>C126*D45</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E126" s="14">
-        <f>C126*E45</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F126" s="14">
-        <f>C126*F45</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G126" s="14">
-        <f>C126*G45</f>
+        <f t="shared" si="32"/>
         <v>68</v>
       </c>
       <c r="H126" s="14">
-        <f>C126*H45</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I126" s="14">
-        <f>C126*I45</f>
+        <f t="shared" si="33"/>
         <v>136</v>
       </c>
       <c r="J126" s="14">
-        <f>C126*J45</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K126" s="14">
-        <f>C126*K45</f>
+        <f t="shared" si="35"/>
         <v>136</v>
       </c>
       <c r="L126" s="14">
-        <f>C126*L45</f>
+        <f t="shared" si="36"/>
         <v>68</v>
       </c>
       <c r="M126" s="14">
-        <f>C126*M45</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N126" s="14">
-        <f>C126*N45</f>
+        <f t="shared" si="37"/>
         <v>68</v>
       </c>
       <c r="O126" s="14"/>
       <c r="P126" s="14"/>
       <c r="Q126" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>476</v>
       </c>
       <c r="R126" s="14">
@@ -7300,57 +7305,57 @@
         <v>58</v>
       </c>
       <c r="C127" s="14">
-        <f>C46*2</f>
+        <f t="shared" si="8"/>
         <v>90</v>
       </c>
       <c r="D127" s="14">
-        <f>C127*D46</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E127" s="14">
-        <f>C127*E46</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F127" s="14">
-        <f>C127*F46</f>
+        <f t="shared" si="31"/>
         <v>90</v>
       </c>
       <c r="G127" s="14">
-        <f>C127*G46</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H127" s="14">
-        <f>C127*H46</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I127" s="14">
-        <f>C127*I46</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J127" s="14">
-        <f>C127*J46</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K127" s="14">
-        <f>C127*K46</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L127" s="14">
-        <f>C127*L46</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M127" s="14">
-        <f>C127*M46</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N127" s="14">
-        <f>C127*N46</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O127" s="14"/>
       <c r="P127" s="14"/>
       <c r="Q127" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>90</v>
       </c>
       <c r="R127" s="14"/>
@@ -7363,57 +7368,57 @@
         <v>144</v>
       </c>
       <c r="C128" s="14">
-        <f>C47*2</f>
+        <f t="shared" si="8"/>
         <v>92</v>
       </c>
       <c r="D128" s="14">
-        <f>C128*D47</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E128" s="14">
-        <f>C128*E47</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F128" s="14">
-        <f>C128*F47</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G128" s="14">
-        <f>C128*G47</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H128" s="14">
-        <f>C128*H47</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I128" s="14">
-        <f>C128*I47</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J128" s="14">
-        <f>C128*J47</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K128" s="14">
-        <f>C128*K47</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L128" s="14">
-        <f>C128*L47</f>
+        <f t="shared" si="36"/>
         <v>92</v>
       </c>
       <c r="M128" s="14">
-        <f>C128*M47</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N128" s="14">
-        <f>C128*N47</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O128" s="14"/>
       <c r="P128" s="14"/>
       <c r="Q128" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>92</v>
       </c>
       <c r="R128" s="14"/>
@@ -7426,57 +7431,57 @@
         <v>60</v>
       </c>
       <c r="C129" s="8">
-        <f t="shared" ref="C129:C147" si="13">C48*2</f>
+        <f t="shared" ref="C129:C147" si="38">C48*2</f>
         <v>264</v>
       </c>
       <c r="D129" s="8">
-        <f>C129*D48</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E129" s="8">
-        <f>C129*E48</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F129" s="8">
-        <f>C129*F48</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G129" s="8">
-        <f>C129*G48</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H129" s="8">
-        <f>C129*H48</f>
+        <f t="shared" si="29"/>
         <v>264</v>
       </c>
       <c r="I129" s="8">
-        <f>C129*I48</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J129" s="8">
-        <f>C129*J48</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K129" s="8">
-        <f>C129*K48</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L129" s="8">
-        <f>C129*L48</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M129" s="8">
-        <f>C129*M48</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N129" s="8">
-        <f>C129*N48</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O129" s="8"/>
       <c r="P129" s="8"/>
       <c r="Q129" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>264</v>
       </c>
       <c r="R129" s="8">
@@ -7505,57 +7510,57 @@
         <v>61</v>
       </c>
       <c r="C130" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="38"/>
         <v>262</v>
       </c>
       <c r="D130" s="8">
-        <f>C130*D49</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E130" s="8">
-        <f>C130*E49</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F130" s="8">
-        <f>C130*F49</f>
+        <f t="shared" si="31"/>
         <v>262</v>
       </c>
       <c r="G130" s="8">
-        <f>C130*G49</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H130" s="8">
-        <f>C130*H49</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I130" s="8">
-        <f>C130*I49</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J130" s="8">
-        <f>C130*J49</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K130" s="8">
-        <f>C130*K49</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L130" s="8">
-        <f>C130*L49</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M130" s="8">
-        <f>C130*M49</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N130" s="8">
-        <f>C130*N49</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O130" s="8"/>
       <c r="P130" s="8"/>
       <c r="Q130" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>262</v>
       </c>
       <c r="R130" s="8"/>
@@ -7581,57 +7586,57 @@
         <v>62</v>
       </c>
       <c r="C131" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="38"/>
         <v>262</v>
       </c>
       <c r="D131" s="8">
-        <f>C131*D50</f>
+        <f t="shared" si="28"/>
         <v>262</v>
       </c>
       <c r="E131" s="8">
-        <f>C131*E50</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F131" s="8">
-        <f>C131*F50</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G131" s="8">
-        <f>C131*G50</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H131" s="8">
-        <f>C131*H50</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I131" s="8">
-        <f>C131*I50</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J131" s="8">
-        <f>C131*J50</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K131" s="8">
-        <f>C131*K50</f>
+        <f t="shared" si="35"/>
         <v>262</v>
       </c>
       <c r="L131" s="8">
-        <f>C131*L50</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M131" s="8">
-        <f>C131*M50</f>
+        <f t="shared" ref="M131:M162" si="39">C131*M50</f>
         <v>0</v>
       </c>
       <c r="N131" s="8">
-        <f>C131*N50</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O131" s="8"/>
       <c r="P131" s="8"/>
       <c r="Q131" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>524</v>
       </c>
       <c r="R131" s="8"/>
@@ -7657,57 +7662,57 @@
         <v>64</v>
       </c>
       <c r="C132" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="38"/>
         <v>272</v>
       </c>
       <c r="D132" s="14">
-        <f>C132*D51</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E132" s="14">
-        <f>C132*E51</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F132" s="14">
-        <f>C132*F51</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G132" s="14">
-        <f>C132*G51</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H132" s="14">
-        <f>C132*H51</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I132" s="14">
-        <f>C132*I51</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J132" s="14">
-        <f>C132*J51</f>
+        <f t="shared" si="34"/>
         <v>544</v>
       </c>
       <c r="K132" s="14">
-        <f>C132*K51</f>
+        <f t="shared" si="35"/>
         <v>272</v>
       </c>
       <c r="L132" s="14">
-        <f>C132*L51</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M132" s="14">
-        <f>C132*M51</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N132" s="14">
-        <f>C132*N51</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O132" s="14"/>
       <c r="P132" s="14"/>
       <c r="Q132" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>816</v>
       </c>
       <c r="R132" s="14">
@@ -7723,57 +7728,57 @@
         <v>66</v>
       </c>
       <c r="C133" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="38"/>
         <v>266</v>
       </c>
       <c r="D133" s="8">
-        <f>C133*D52</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E133" s="8">
-        <f>C133*E52</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F133" s="8">
-        <f>C133*F52</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G133" s="8">
-        <f>C133*G52</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H133" s="8">
-        <f>C133*H52</f>
+        <f t="shared" si="29"/>
         <v>266</v>
       </c>
       <c r="I133" s="8">
-        <f>C133*I52</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J133" s="8">
-        <f>C133*J52</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K133" s="8">
-        <f>C133*K52</f>
+        <f t="shared" si="35"/>
         <v>266</v>
       </c>
       <c r="L133" s="8">
-        <f>C133*L52</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M133" s="8">
-        <f>C133*M52</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N133" s="8">
-        <f>C133*N52</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O133" s="8"/>
       <c r="P133" s="8"/>
       <c r="Q133" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>532</v>
       </c>
       <c r="R133" s="8">
@@ -7802,57 +7807,57 @@
         <v>67</v>
       </c>
       <c r="C134" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="38"/>
         <v>304</v>
       </c>
       <c r="D134" s="8">
-        <f>C134*D53</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E134" s="8">
-        <f>C134*E53</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F134" s="8">
-        <f>C134*F53</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G134" s="8">
-        <f>C134*G53</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H134" s="8">
-        <f>C134*H53</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I134" s="8">
-        <f>C134*I53</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J134" s="8">
-        <f>C134*J53</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K134" s="8">
-        <f>C134*K53</f>
+        <f t="shared" si="35"/>
         <v>304</v>
       </c>
       <c r="L134" s="8">
-        <f>C134*L53</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M134" s="8">
-        <f>C134*M53</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N134" s="8">
-        <f>C134*N53</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O134" s="8"/>
       <c r="P134" s="8"/>
       <c r="Q134" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>304</v>
       </c>
       <c r="R134" s="8"/>
@@ -7878,57 +7883,57 @@
         <v>68</v>
       </c>
       <c r="C135" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="38"/>
         <v>254</v>
       </c>
       <c r="D135" s="8">
-        <f>C135*D54</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E135" s="8">
-        <f>C135*E54</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F135" s="8">
-        <f>C135*F54</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G135" s="8">
-        <f>C135*G54</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H135" s="8">
-        <f>C135*H54</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I135" s="8">
-        <f>C135*I54</f>
+        <f t="shared" si="33"/>
         <v>254</v>
       </c>
       <c r="J135" s="8">
-        <f>C135*J54</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K135" s="8">
-        <f>C135*K54</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L135" s="8">
-        <f>C135*L54</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M135" s="8">
-        <f>C135*M54</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N135" s="8">
-        <f>C135*N54</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O135" s="8"/>
       <c r="P135" s="8"/>
       <c r="Q135" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>254</v>
       </c>
       <c r="R135" s="8"/>
@@ -7954,57 +7959,57 @@
         <v>69</v>
       </c>
       <c r="C136" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="38"/>
         <v>306</v>
       </c>
       <c r="D136" s="8">
-        <f>C136*D55</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E136" s="8">
-        <f>C136*E55</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F136" s="8">
-        <f>C136*F55</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G136" s="8">
-        <f>C136*G55</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H136" s="8">
-        <f>C136*H55</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I136" s="8">
-        <f>C136*I55</f>
+        <f t="shared" si="33"/>
         <v>306</v>
       </c>
       <c r="J136" s="8">
-        <f>C136*J55</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K136" s="8">
-        <f>C136*K55</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L136" s="8">
-        <f>C136*L55</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M136" s="8">
-        <f>C136*M55</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N136" s="8">
-        <f>C136*N55</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O136" s="8"/>
       <c r="P136" s="8"/>
       <c r="Q136" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>306</v>
       </c>
       <c r="R136" s="8"/>
@@ -8030,57 +8035,57 @@
         <v>71</v>
       </c>
       <c r="C137" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="38"/>
         <v>124</v>
       </c>
       <c r="D137" s="14">
-        <f>C137*D56</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E137" s="14">
-        <f>C137*E56</f>
+        <f t="shared" si="30"/>
         <v>124</v>
       </c>
       <c r="F137" s="14">
-        <f>C137*F56</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G137" s="14">
-        <f>C137*G56</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H137" s="14">
-        <f>C137*H56</f>
+        <f t="shared" si="29"/>
         <v>124</v>
       </c>
       <c r="I137" s="14">
-        <f>C137*I56</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J137" s="14">
-        <f>C137*J56</f>
+        <f t="shared" si="34"/>
         <v>248</v>
       </c>
       <c r="K137" s="14">
-        <f>C137*K56</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L137" s="14">
-        <f>C137*L56</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M137" s="14">
-        <f>C137*M56</f>
+        <f t="shared" si="39"/>
         <v>124</v>
       </c>
       <c r="N137" s="14">
-        <f>C137*N56</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O137" s="14"/>
       <c r="P137" s="14"/>
       <c r="Q137" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>620</v>
       </c>
       <c r="R137" s="14">
@@ -8096,57 +8101,57 @@
         <v>72</v>
       </c>
       <c r="C138" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="38"/>
         <v>130</v>
       </c>
       <c r="D138" s="14">
-        <f>C138*D57</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E138" s="14">
-        <f>C138*E57</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F138" s="14">
-        <f>C138*F57</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G138" s="14">
-        <f>C138*G57</f>
+        <f t="shared" si="32"/>
         <v>260</v>
       </c>
       <c r="H138" s="14">
-        <f>C138*H57</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I138" s="14">
-        <f>C138*I57</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J138" s="14">
-        <f>C138*J57</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K138" s="14">
-        <f>C138*K57</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L138" s="14">
-        <f>C138*L57</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M138" s="14">
-        <f>C138*M57</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N138" s="14">
-        <f>C138*N57</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O138" s="14"/>
       <c r="P138" s="14"/>
       <c r="Q138" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>260</v>
       </c>
       <c r="R138" s="14"/>
@@ -8159,57 +8164,57 @@
         <v>73</v>
       </c>
       <c r="C139" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="38"/>
         <v>124</v>
       </c>
       <c r="D139" s="14">
-        <f>C139*D58</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E139" s="14">
-        <f>C139*E58</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F139" s="14">
-        <f>C139*F58</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G139" s="14">
-        <f>C139*G58</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H139" s="14">
-        <f>C139*H58</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I139" s="14">
-        <f>C139*I58</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J139" s="14">
-        <f>C139*J58</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K139" s="14">
-        <f>C139*K58</f>
+        <f t="shared" si="35"/>
         <v>124</v>
       </c>
       <c r="L139" s="14">
-        <f>C139*L58</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M139" s="14">
-        <f>C139*M58</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N139" s="14">
-        <f>C139*N58</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O139" s="14"/>
       <c r="P139" s="14"/>
       <c r="Q139" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>124</v>
       </c>
       <c r="R139" s="14"/>
@@ -8222,57 +8227,57 @@
         <v>124</v>
       </c>
       <c r="C140" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="38"/>
         <v>90</v>
       </c>
       <c r="D140" s="8">
-        <f>C140*D59</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E140" s="8">
-        <f>C140*E59</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F140" s="8">
-        <f>C140*F59</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G140" s="8">
-        <f>C140*G59</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H140" s="8">
-        <f>C140*H59</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I140" s="8">
-        <f>C140*I59</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J140" s="8">
-        <f>C140*J59</f>
+        <f t="shared" si="34"/>
         <v>90</v>
       </c>
       <c r="K140" s="8">
-        <f>C140*K59</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L140" s="8">
-        <f>C140*L59</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M140" s="8">
-        <f>C140*M59</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N140" s="8">
-        <f>C140*N59</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O140" s="8"/>
       <c r="P140" s="8"/>
       <c r="Q140" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>90</v>
       </c>
       <c r="R140" s="8">
@@ -8301,57 +8306,57 @@
         <v>76</v>
       </c>
       <c r="C141" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="38"/>
         <v>106</v>
       </c>
       <c r="D141" s="8">
-        <f>C141*D60</f>
+        <f t="shared" si="28"/>
         <v>106</v>
       </c>
       <c r="E141" s="8">
-        <f>C141*E60</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F141" s="8">
-        <f>C141*F60</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G141" s="8">
-        <f>C141*G60</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H141" s="8">
-        <f>C141*H60</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I141" s="8">
-        <f>C141*I60</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J141" s="8">
-        <f>C141*J60</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K141" s="8">
-        <f>C141*K60</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L141" s="8">
-        <f>C141*L60</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M141" s="8">
-        <f>C141*M60</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N141" s="8">
-        <f>C141*N60</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O141" s="8"/>
       <c r="P141" s="8"/>
       <c r="Q141" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>106</v>
       </c>
       <c r="R141" s="8"/>
@@ -8377,57 +8382,57 @@
         <v>77</v>
       </c>
       <c r="C142" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="38"/>
         <v>90</v>
       </c>
       <c r="D142" s="8">
-        <f>C142*D61</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E142" s="8">
-        <f>C142*E61</f>
+        <f t="shared" si="30"/>
         <v>90</v>
       </c>
       <c r="F142" s="8">
-        <f>C142*F61</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G142" s="8">
-        <f>C142*G61</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H142" s="8">
-        <f>C142*H61</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I142" s="8">
-        <f>C142*I61</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J142" s="8">
-        <f>C142*J61</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K142" s="8">
-        <f>C142*K61</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L142" s="8">
-        <f>C142*L61</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M142" s="8">
-        <f>C142*M61</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N142" s="8">
-        <f>C142*N61</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O142" s="8"/>
       <c r="P142" s="8"/>
       <c r="Q142" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>90</v>
       </c>
       <c r="R142" s="8"/>
@@ -8453,57 +8458,57 @@
         <v>79</v>
       </c>
       <c r="C143" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="38"/>
         <v>40</v>
       </c>
       <c r="D143" s="14">
-        <f>C143*D62</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E143" s="14">
-        <f>C143*E62</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F143" s="14">
-        <f>C143*F62</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G143" s="14">
-        <f>C143*G62</f>
+        <f t="shared" si="32"/>
         <v>80</v>
       </c>
       <c r="H143" s="14">
-        <f>C143*H62</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I143" s="14">
-        <f>C143*I62</f>
+        <f t="shared" si="33"/>
         <v>160</v>
       </c>
       <c r="J143" s="14">
-        <f>C143*J62</f>
+        <f t="shared" si="34"/>
         <v>160</v>
       </c>
       <c r="K143" s="14">
-        <f>C143*K62</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="L143" s="14">
-        <f>C143*L62</f>
+        <f t="shared" si="36"/>
         <v>40</v>
       </c>
       <c r="M143" s="14">
-        <f>C143*M62</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N143" s="14">
-        <f>C143*N62</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O143" s="14"/>
       <c r="P143" s="14"/>
       <c r="Q143" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>440</v>
       </c>
       <c r="R143" s="14">
@@ -8519,57 +8524,57 @@
         <v>80</v>
       </c>
       <c r="C144" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="38"/>
         <v>34</v>
       </c>
       <c r="D144" s="14">
-        <f>C144*D63</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="E144" s="14">
-        <f>C144*E63</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F144" s="14">
-        <f>C144*F63</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G144" s="14">
-        <f>C144*G63</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H144" s="14">
-        <f>C144*H63</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I144" s="14">
-        <f>C144*I63</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J144" s="14">
-        <f>C144*J63</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K144" s="14">
-        <f>C144*K63</f>
+        <f t="shared" si="35"/>
         <v>136</v>
       </c>
       <c r="L144" s="14">
-        <f>C144*L63</f>
+        <f t="shared" si="36"/>
         <v>68</v>
       </c>
       <c r="M144" s="14">
-        <f>C144*M63</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N144" s="14">
-        <f>C144*N63</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O144" s="14"/>
       <c r="P144" s="14"/>
       <c r="Q144" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>204</v>
       </c>
       <c r="R144" s="14"/>
@@ -8582,7 +8587,7 @@
         <v>102</v>
       </c>
       <c r="C145" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="38"/>
         <v>34</v>
       </c>
       <c r="D145" s="14">
@@ -8610,21 +8615,21 @@
         <v>0</v>
       </c>
       <c r="L145" s="14">
-        <f>C145*L64</f>
+        <f t="shared" si="36"/>
         <v>68</v>
       </c>
       <c r="M145" s="14">
-        <f>C145*M64</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N145" s="14">
-        <f>C145*N64</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O145" s="14"/>
       <c r="P145" s="14"/>
       <c r="Q145" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>68</v>
       </c>
       <c r="R145" s="14"/>
@@ -8637,57 +8642,57 @@
         <v>82</v>
       </c>
       <c r="C146" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="38"/>
         <v>248</v>
       </c>
       <c r="D146" s="8">
-        <f>C146*D65</f>
+        <f t="shared" ref="D146:D151" si="40">C146*D65</f>
         <v>248</v>
       </c>
       <c r="E146" s="8">
-        <f>C146*E65</f>
+        <f t="shared" ref="E146:E151" si="41">C146*E65</f>
         <v>248</v>
       </c>
       <c r="F146" s="8">
-        <f>C146*F65</f>
+        <f t="shared" ref="F146:F151" si="42">C146*F65</f>
         <v>248</v>
       </c>
       <c r="G146" s="8">
-        <f>C146*G65</f>
+        <f t="shared" ref="G146:G151" si="43">C146*G65</f>
         <v>496</v>
       </c>
       <c r="H146" s="8">
-        <f>C146*H65</f>
+        <f t="shared" ref="H146:H151" si="44">C146*H65</f>
         <v>0</v>
       </c>
       <c r="I146" s="8">
-        <f>C146*I65</f>
+        <f t="shared" ref="I146:I151" si="45">C146*I65</f>
         <v>0</v>
       </c>
       <c r="J146" s="8">
-        <f>C146*J65</f>
+        <f t="shared" ref="J146:J151" si="46">C146*J65</f>
         <v>0</v>
       </c>
       <c r="K146" s="8">
-        <f>C146*K65</f>
+        <f t="shared" ref="K146:K151" si="47">C146*K65</f>
         <v>0</v>
       </c>
       <c r="L146" s="8">
-        <f>C146*L65</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M146" s="8">
-        <f>C146*M65</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N146" s="8">
-        <f>C146*N65</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O146" s="8"/>
       <c r="P146" s="8"/>
       <c r="Q146" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1240</v>
       </c>
       <c r="R146" s="8">
@@ -8716,57 +8721,57 @@
         <v>84</v>
       </c>
       <c r="C147" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="38"/>
         <v>124</v>
       </c>
       <c r="D147" s="14">
-        <f>C147*D66</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="E147" s="14">
-        <f>C147*E66</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="F147" s="14">
-        <f>C147*F66</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="G147" s="14">
-        <f>C147*G66</f>
+        <f t="shared" si="43"/>
         <v>124</v>
       </c>
       <c r="H147" s="14">
-        <f>C147*H66</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="I147" s="14">
-        <f>C147*I66</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="J147" s="14">
-        <f>C147*J66</f>
+        <f t="shared" si="46"/>
         <v>124</v>
       </c>
       <c r="K147" s="14">
-        <f>C147*K66</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="L147" s="14">
-        <f>C147*L66</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M147" s="14">
-        <f>C147*M66</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N147" s="14">
-        <f>C147*N66</f>
+        <f t="shared" ref="N147:N178" si="48">C147*N66</f>
         <v>0</v>
       </c>
       <c r="O147" s="14"/>
       <c r="P147" s="14"/>
       <c r="Q147" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>248</v>
       </c>
       <c r="R147" s="14">
@@ -8782,57 +8787,57 @@
         <v>85</v>
       </c>
       <c r="C148" s="14">
-        <f t="shared" ref="C148:C179" si="14">C67*2</f>
+        <f t="shared" ref="C148:C151" si="49">C67*2</f>
         <v>118</v>
       </c>
       <c r="D148" s="14">
-        <f>C148*D67</f>
+        <f t="shared" si="40"/>
         <v>118</v>
       </c>
       <c r="E148" s="14">
-        <f>C148*E67</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="F148" s="14">
-        <f>C148*F67</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="G148" s="14">
-        <f>C148*G67</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="H148" s="14">
-        <f>C148*H67</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="I148" s="14">
-        <f>C148*I67</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="J148" s="14">
-        <f>C148*J67</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="K148" s="14">
-        <f>C148*K67</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="L148" s="14">
-        <f>C148*L67</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M148" s="14">
-        <f>C148*M67</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N148" s="14">
-        <f>C148*N67</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="O148" s="14"/>
       <c r="P148" s="14"/>
       <c r="Q148" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>118</v>
       </c>
       <c r="R148" s="14"/>
@@ -8845,57 +8850,57 @@
         <v>86</v>
       </c>
       <c r="C149" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="49"/>
         <v>116</v>
       </c>
       <c r="D149" s="14">
-        <f>C149*D68</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="E149" s="14">
-        <f>C149*E68</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="F149" s="14">
-        <f>C149*F68</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="G149" s="14">
-        <f>C149*G68</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="H149" s="14">
-        <f>C149*H68</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="I149" s="14">
-        <f>C149*I68</f>
+        <f t="shared" si="45"/>
         <v>116</v>
       </c>
       <c r="J149" s="14">
-        <f>C149*J68</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="K149" s="14">
-        <f>C149*K68</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="L149" s="14">
-        <f>C149*L68</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M149" s="14">
-        <f>C149*M68</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N149" s="14">
-        <f>C149*N68</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="O149" s="14"/>
       <c r="P149" s="14"/>
       <c r="Q149" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>116</v>
       </c>
       <c r="R149" s="14"/>
@@ -8908,57 +8913,57 @@
         <v>88</v>
       </c>
       <c r="C150" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="49"/>
         <v>138</v>
       </c>
       <c r="D150" s="8">
-        <f>C150*D69</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="E150" s="8">
-        <f>C150*E69</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="F150" s="8">
-        <f>C150*F69</f>
+        <f t="shared" si="42"/>
         <v>138</v>
       </c>
       <c r="G150" s="8">
-        <f>C150*G69</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="H150" s="8">
-        <f>C150*H69</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="I150" s="8">
-        <f>C150*I69</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="J150" s="8">
-        <f>C150*J69</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="K150" s="8">
-        <f>C150*K69</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="L150" s="8">
-        <f>C150*L69</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M150" s="8">
-        <f>C150*M69</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N150" s="8">
-        <f>C150*N69</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="O150" s="8"/>
       <c r="P150" s="8"/>
       <c r="Q150" s="8">
-        <f t="shared" ref="Q150:Q151" si="15">SUM(D150:N150)</f>
+        <f t="shared" ref="Q150:Q151" si="50">SUM(D150:N150)</f>
         <v>138</v>
       </c>
       <c r="R150" s="8">
@@ -8987,57 +8992,57 @@
         <v>137</v>
       </c>
       <c r="C151" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="49"/>
         <v>376</v>
       </c>
       <c r="D151" s="14">
-        <f>C151*D70</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="E151" s="14">
-        <f>C151*E70</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="F151" s="14">
-        <f>C151*F70</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="G151" s="14">
-        <f>C151*G70</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="H151" s="14">
-        <f>C151*H70</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="I151" s="14">
-        <f>C151*I70</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="J151" s="14">
-        <f>C151*J70</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="K151" s="14">
-        <f>C151*K70</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="L151" s="14">
-        <f>C151*L70</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M151" s="14">
-        <f>C151*M70</f>
+        <f t="shared" si="39"/>
         <v>376</v>
       </c>
       <c r="N151" s="14">
-        <f>C151*N70</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="O151" s="6"/>
       <c r="P151" s="6"/>
       <c r="Q151" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="50"/>
         <v>376</v>
       </c>
       <c r="R151" s="14">
@@ -9102,60 +9107,60 @@
         <v>750</v>
       </c>
       <c r="E155" s="8">
-        <f t="shared" ref="E155:N155" si="16">SUM(E83:E151)</f>
+        <f t="shared" ref="E155:N155" si="51">SUM(E83:E151)</f>
         <v>892</v>
       </c>
       <c r="F155" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="51"/>
         <v>1166</v>
       </c>
       <c r="G155" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="51"/>
         <v>1830</v>
       </c>
       <c r="H155" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="51"/>
         <v>802</v>
       </c>
       <c r="I155" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="51"/>
         <v>3046</v>
       </c>
       <c r="J155" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="51"/>
         <v>2704</v>
       </c>
       <c r="K155" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="51"/>
         <v>4664</v>
       </c>
       <c r="L155" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="51"/>
         <v>2746</v>
       </c>
       <c r="M155" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="51"/>
         <v>7380</v>
       </c>
       <c r="N155" s="8">
-        <f t="shared" si="16"/>
-        <v>122</v>
+        <f t="shared" si="51"/>
+        <v>492</v>
       </c>
       <c r="O155" s="8">
         <f>SUM(D155:N155)</f>
-        <v>26102</v>
+        <v>26472</v>
       </c>
       <c r="P155" s="15">
         <f>O155/O72</f>
-        <v>155.36904761904762</v>
+        <v>157.57142857142858</v>
       </c>
       <c r="Q155" s="8">
         <f>SUM(Q83:Q151)</f>
-        <v>26102</v>
+        <v>26472</v>
       </c>
       <c r="R155" s="8">
         <f>SUM(R83:R151)</f>
-        <v>26102</v>
+        <v>26472</v>
       </c>
     </row>
     <row r="156" spans="1:31" x14ac:dyDescent="0.3">
@@ -9163,52 +9168,52 @@
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
       <c r="D156" s="16">
-        <f t="shared" ref="D156:O156" si="17">D155/D72</f>
+        <f t="shared" ref="D156:O156" si="52">D155/D72</f>
         <v>150</v>
       </c>
       <c r="E156" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="52"/>
         <v>89.2</v>
       </c>
       <c r="F156" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="52"/>
         <v>116.6</v>
       </c>
       <c r="G156" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="52"/>
         <v>114.375</v>
       </c>
       <c r="H156" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="52"/>
         <v>160.4</v>
       </c>
       <c r="I156" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="52"/>
         <v>138.45454545454547</v>
       </c>
       <c r="J156" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="52"/>
         <v>142.31578947368422</v>
       </c>
       <c r="K156" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="52"/>
         <v>172.74074074074073</v>
       </c>
       <c r="L156" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="52"/>
         <v>161.52941176470588</v>
       </c>
       <c r="M156" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="52"/>
         <v>199.45945945945945</v>
       </c>
       <c r="N156" s="16" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="52"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O156" s="16">
-        <f t="shared" si="17"/>
-        <v>155.36904761904762</v>
+        <f t="shared" si="52"/>
+        <v>157.57142857142858</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>97</v>
@@ -9342,11 +9347,11 @@
       </c>
       <c r="C166" s="8">
         <f>SUM(O18:O19)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D166" s="8">
         <f>R99</f>
-        <v>1202</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
@@ -9396,7 +9401,7 @@
         <v>1</v>
       </c>
       <c r="D169" s="14">
-        <f t="shared" ref="D169:D175" si="18">R107</f>
+        <f t="shared" ref="D169:D175" si="53">R107</f>
         <v>800</v>
       </c>
     </row>
@@ -9413,7 +9418,7 @@
         <v>1</v>
       </c>
       <c r="D170" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="53"/>
         <v>726</v>
       </c>
     </row>
@@ -9430,7 +9435,7 @@
         <v>1</v>
       </c>
       <c r="D171" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="53"/>
         <v>186</v>
       </c>
     </row>
@@ -9447,7 +9452,7 @@
         <v>1</v>
       </c>
       <c r="D172" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="53"/>
         <v>348</v>
       </c>
     </row>
@@ -9464,7 +9469,7 @@
         <v>1</v>
       </c>
       <c r="D173" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="53"/>
         <v>418</v>
       </c>
     </row>
@@ -9481,7 +9486,7 @@
         <v>1</v>
       </c>
       <c r="D174" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="53"/>
         <v>516</v>
       </c>
     </row>
@@ -9498,7 +9503,7 @@
         <v>32</v>
       </c>
       <c r="D175" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="53"/>
         <v>1768</v>
       </c>
     </row>
@@ -9775,18 +9780,18 @@
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A192" s="21"/>
-      <c r="B192" s="21">
+      <c r="A192" s="20"/>
+      <c r="B192" s="20">
         <f>SUM(B160:B191)</f>
         <v>69</v>
       </c>
-      <c r="C192" s="21">
+      <c r="C192" s="20">
         <f>SUM(C160:C191)</f>
-        <v>170</v>
-      </c>
-      <c r="D192" s="21">
+        <v>171</v>
+      </c>
+      <c r="D192" s="20">
         <f>SUM(D160:D191)</f>
-        <v>25726</v>
+        <v>26096</v>
       </c>
     </row>
   </sheetData>
@@ -9963,7 +9968,7 @@
       <c r="A6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>138</v>
       </c>
       <c r="C6" s="8">
@@ -10025,7 +10030,7 @@
       <c r="A8" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>141</v>
       </c>
       <c r="C8" s="8">
@@ -10089,7 +10094,7 @@
       <c r="A10" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="22" t="s">
         <v>115</v>
       </c>
       <c r="C10" s="8">
@@ -10560,7 +10565,7 @@
       <c r="A30" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="22" t="s">
         <v>115</v>
       </c>
       <c r="C30" s="8">

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14DCB8BA-414F-4489-BAA2-5FDFD30A1D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B83B2D-C855-4DC9-827E-6CCFEEDC323D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
@@ -2990,18 +2990,20 @@
         <v>1</v>
       </c>
       <c r="M47" s="14"/>
-      <c r="N47" s="14"/>
+      <c r="N47" s="14">
+        <v>1</v>
+      </c>
       <c r="O47" s="14">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P47" s="14">
         <f t="shared" si="4"/>
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="Q47" s="14">
         <f t="shared" si="1"/>
-        <v>92</v>
+        <v>184</v>
       </c>
       <c r="R47" s="14"/>
     </row>
@@ -4080,15 +4082,15 @@
       <c r="N71" s="6"/>
       <c r="O71" s="6">
         <f>SUM(O2:O70)</f>
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P71" s="6">
         <f>SUM(P2:P70)</f>
-        <v>13236</v>
+        <v>13282</v>
       </c>
       <c r="Q71" s="6">
         <f>SUM(Q2:Q70)</f>
-        <v>26472</v>
+        <v>26564</v>
       </c>
       <c r="R71" s="6"/>
     </row>
@@ -4146,7 +4148,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="7">
         <f>SUM(Q2:Q70)</f>
-        <v>26472</v>
+        <v>26564</v>
       </c>
       <c r="R72" s="13">
         <f>SUM(R2:R70)</f>
@@ -7294,7 +7296,7 @@
       </c>
       <c r="R126" s="14">
         <f>SUM(Q126:Q128)</f>
-        <v>658</v>
+        <v>750</v>
       </c>
     </row>
     <row r="127" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
@@ -7413,13 +7415,13 @@
       </c>
       <c r="N128" s="14">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="O128" s="14"/>
       <c r="P128" s="14"/>
       <c r="Q128" s="14">
         <f t="shared" si="12"/>
-        <v>92</v>
+        <v>184</v>
       </c>
       <c r="R128" s="14"/>
     </row>
@@ -7626,7 +7628,7 @@
         <v>0</v>
       </c>
       <c r="M131" s="8">
-        <f t="shared" ref="M131:M162" si="39">C131*M50</f>
+        <f t="shared" ref="M131:M151" si="39">C131*M50</f>
         <v>0</v>
       </c>
       <c r="N131" s="8">
@@ -8765,7 +8767,7 @@
         <v>0</v>
       </c>
       <c r="N147" s="14">
-        <f t="shared" ref="N147:N178" si="48">C147*N66</f>
+        <f t="shared" ref="N147:N151" si="48">C147*N66</f>
         <v>0</v>
       </c>
       <c r="O147" s="14"/>
@@ -9144,23 +9146,23 @@
       </c>
       <c r="N155" s="8">
         <f t="shared" si="51"/>
-        <v>492</v>
+        <v>584</v>
       </c>
       <c r="O155" s="8">
         <f>SUM(D155:N155)</f>
-        <v>26472</v>
+        <v>26564</v>
       </c>
       <c r="P155" s="15">
         <f>O155/O72</f>
-        <v>157.57142857142858</v>
+        <v>158.11904761904762</v>
       </c>
       <c r="Q155" s="8">
         <f>SUM(Q83:Q151)</f>
-        <v>26472</v>
+        <v>26564</v>
       </c>
       <c r="R155" s="8">
         <f>SUM(R83:R151)</f>
-        <v>26472</v>
+        <v>26564</v>
       </c>
     </row>
     <row r="156" spans="1:31" x14ac:dyDescent="0.3">
@@ -9213,7 +9215,7 @@
       </c>
       <c r="O156" s="16">
         <f t="shared" si="52"/>
-        <v>157.57142857142858</v>
+        <v>158.11904761904762</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>97</v>
@@ -9606,7 +9608,7 @@
       </c>
       <c r="D181" s="14">
         <f>R126</f>
-        <v>658</v>
+        <v>750</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
@@ -9791,7 +9793,7 @@
       </c>
       <c r="D192" s="20">
         <f>SUM(D160:D191)</f>
-        <v>26096</v>
+        <v>26188</v>
       </c>
     </row>
   </sheetData>

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B83B2D-C855-4DC9-827E-6CCFEEDC323D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DD2741-4A69-416A-9860-21289772963C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
@@ -474,7 +474,7 @@
     <t>Vapaa-aikakeskus</t>
   </si>
   <si>
-    <t>3.10.2026</t>
+    <t>18.10.2026</t>
   </si>
 </sst>
 </file>
@@ -1114,18 +1114,20 @@
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
+      <c r="N4" s="8">
+        <v>1</v>
+      </c>
       <c r="O4" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q4" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R4" s="8"/>
     </row>
@@ -3473,18 +3475,20 @@
       <c r="K57" s="14"/>
       <c r="L57" s="14"/>
       <c r="M57" s="14"/>
-      <c r="N57" s="14"/>
+      <c r="N57" s="14">
+        <v>1</v>
+      </c>
       <c r="O57" s="14">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P57" s="14">
         <f t="shared" si="4"/>
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Q57" s="14">
         <f t="shared" si="1"/>
-        <v>260</v>
+        <v>390</v>
       </c>
       <c r="R57" s="14"/>
     </row>
@@ -4082,15 +4086,15 @@
       <c r="N71" s="6"/>
       <c r="O71" s="6">
         <f>SUM(O2:O70)</f>
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="P71" s="6">
         <f>SUM(P2:P70)</f>
-        <v>13282</v>
+        <v>13351</v>
       </c>
       <c r="Q71" s="6">
         <f>SUM(Q2:Q70)</f>
-        <v>26564</v>
+        <v>26702</v>
       </c>
       <c r="R71" s="6"/>
     </row>
@@ -4148,7 +4152,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="7">
         <f>SUM(Q2:Q70)</f>
-        <v>26564</v>
+        <v>26702</v>
       </c>
       <c r="R72" s="13">
         <f>SUM(R2:R70)</f>
@@ -4446,7 +4450,7 @@
       </c>
       <c r="R83" s="8">
         <f>SUM(Q83:Q86)</f>
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.3">
@@ -4565,13 +4569,13 @@
       </c>
       <c r="N85" s="8">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O85" s="8"/>
       <c r="P85" s="8"/>
       <c r="Q85" s="8">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R85" s="8"/>
     </row>
@@ -8092,7 +8096,7 @@
       </c>
       <c r="R137" s="14">
         <f>SUM(Q137:Q139)</f>
-        <v>1004</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="138" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
@@ -8148,13 +8152,13 @@
       </c>
       <c r="N138" s="14">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="O138" s="14"/>
       <c r="P138" s="14"/>
       <c r="Q138" s="14">
         <f t="shared" si="12"/>
-        <v>260</v>
+        <v>390</v>
       </c>
       <c r="R138" s="14"/>
     </row>
@@ -9146,23 +9150,23 @@
       </c>
       <c r="N155" s="8">
         <f t="shared" si="51"/>
-        <v>584</v>
+        <v>722</v>
       </c>
       <c r="O155" s="8">
         <f>SUM(D155:N155)</f>
-        <v>26564</v>
+        <v>26702</v>
       </c>
       <c r="P155" s="15">
         <f>O155/O72</f>
-        <v>158.11904761904762</v>
+        <v>158.9404761904762</v>
       </c>
       <c r="Q155" s="8">
         <f>SUM(Q83:Q151)</f>
-        <v>26564</v>
+        <v>26702</v>
       </c>
       <c r="R155" s="8">
         <f>SUM(R83:R151)</f>
-        <v>26564</v>
+        <v>26702</v>
       </c>
     </row>
     <row r="156" spans="1:31" x14ac:dyDescent="0.3">
@@ -9215,7 +9219,7 @@
       </c>
       <c r="O156" s="16">
         <f t="shared" si="52"/>
-        <v>158.11904761904762</v>
+        <v>158.9404761904762</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>97</v>
@@ -9247,11 +9251,11 @@
       </c>
       <c r="C160" s="8">
         <f>SUM(O2:O5)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D160" s="8">
         <f>R83</f>
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
@@ -9672,11 +9676,11 @@
       </c>
       <c r="C185" s="14">
         <f>SUM(O56:O58)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D185" s="14">
         <f>R137</f>
-        <v>1004</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
@@ -9789,11 +9793,11 @@
       </c>
       <c r="C192" s="20">
         <f>SUM(C160:C191)</f>
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D192" s="20">
         <f>SUM(D160:D191)</f>
-        <v>26188</v>
+        <v>26326</v>
       </c>
     </row>
   </sheetData>

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DD2741-4A69-416A-9860-21289772963C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA3636F-6C09-41D1-99E2-FA0F490EAC3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
+    <workbookView xWindow="4152" yWindow="1068" windowWidth="17280" windowHeight="11580" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
   <sheets>
     <sheet name="pelipaikat" sheetId="1" r:id="rId1"/>
@@ -474,7 +474,7 @@
     <t>Vapaa-aikakeskus</t>
   </si>
   <si>
-    <t>18.10.2026</t>
+    <t>25.10.2026</t>
   </si>
 </sst>
 </file>
@@ -2308,18 +2308,20 @@
       </c>
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
+      <c r="N32" s="14">
+        <v>1</v>
+      </c>
       <c r="O32" s="14">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P32" s="14">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="Q32" s="14">
         <f t="shared" ref="Q32:Q37" si="3">2*P32</f>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="R32" s="14">
         <v>6</v>
@@ -4086,15 +4088,15 @@
       <c r="N71" s="6"/>
       <c r="O71" s="6">
         <f>SUM(O2:O70)</f>
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P71" s="6">
         <f>SUM(P2:P70)</f>
-        <v>13351</v>
+        <v>13376</v>
       </c>
       <c r="Q71" s="6">
         <f>SUM(Q2:Q70)</f>
-        <v>26702</v>
+        <v>26752</v>
       </c>
       <c r="R71" s="6"/>
     </row>
@@ -4152,7 +4154,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="7">
         <f>SUM(Q2:Q70)</f>
-        <v>26702</v>
+        <v>26752</v>
       </c>
       <c r="R72" s="13">
         <f>SUM(R2:R70)</f>
@@ -6388,17 +6390,17 @@
       </c>
       <c r="N113" s="14">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O113" s="14"/>
       <c r="P113" s="14"/>
       <c r="Q113" s="14">
         <f t="shared" si="12"/>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="R113" s="14">
         <f>SUM(Q113:Q118)</f>
-        <v>1768</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="114" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
@@ -9150,23 +9152,23 @@
       </c>
       <c r="N155" s="8">
         <f t="shared" si="51"/>
-        <v>722</v>
+        <v>772</v>
       </c>
       <c r="O155" s="8">
         <f>SUM(D155:N155)</f>
-        <v>26702</v>
+        <v>26752</v>
       </c>
       <c r="P155" s="15">
         <f>O155/O72</f>
-        <v>158.9404761904762</v>
+        <v>159.23809523809524</v>
       </c>
       <c r="Q155" s="8">
         <f>SUM(Q83:Q151)</f>
-        <v>26702</v>
+        <v>26752</v>
       </c>
       <c r="R155" s="8">
         <f>SUM(R83:R151)</f>
-        <v>26702</v>
+        <v>26752</v>
       </c>
     </row>
     <row r="156" spans="1:31" x14ac:dyDescent="0.3">
@@ -9219,7 +9221,7 @@
       </c>
       <c r="O156" s="16">
         <f t="shared" si="52"/>
-        <v>158.9404761904762</v>
+        <v>159.23809523809524</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>97</v>
@@ -9506,11 +9508,11 @@
       </c>
       <c r="C175" s="14">
         <f>SUM(O32:O37)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D175" s="14">
         <f t="shared" si="53"/>
-        <v>1768</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
@@ -9793,11 +9795,11 @@
       </c>
       <c r="C192" s="20">
         <f>SUM(C160:C191)</f>
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D192" s="20">
         <f>SUM(D160:D191)</f>
-        <v>26326</v>
+        <v>26376</v>
       </c>
     </row>
   </sheetData>
